--- a/outputs/daily/predictions_2026-06-16.xlsx
+++ b/outputs/daily/predictions_2026-06-16.xlsx
@@ -843,31 +843,31 @@
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>1.909106316454173</v>
+        <v>1.912173533505455</v>
       </c>
       <c r="L2" t="n">
-        <v>0.9051383061545761</v>
+        <v>0.9075710891032949</v>
       </c>
       <c r="M2" t="b">
         <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6535584266096387</v>
+        <v>0.6527282379235715</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2122958888332656</v>
+        <v>0.2124939722984123</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1341456845570958</v>
+        <v>0.1347777897780163</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.540589892804359</v>
+        <v>0.5430904977157262</v>
       </c>
       <c r="R2" t="n">
-        <v>2.028626962990445</v>
+        <v>2.034203721265502</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8113730370095551</v>
+        <v>0.8157962787344981</v>
       </c>
       <c r="T2" t="n">
         <v>0.6824643606071525</v>
@@ -876,7 +876,7 @@
         <v>0.1775220392121052</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1400136001807423</v>
+        <v>0.1400136001807424</v>
       </c>
       <c r="W2" t="n">
         <v>0.5487541995078554</v>
@@ -885,58 +885,58 @@
         <v>0.4953723824956653</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.598809727959816</v>
+        <v>0.5988912617371379</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.2386045207765079</v>
+        <v>0.2383388564445202</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.1625857512636756</v>
+        <v>0.1627698818183422</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.5339324333415528</v>
+        <v>0.5352370688833286</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.4660675666584472</v>
+        <v>0.4647629311166714</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.5176102321261974</v>
+        <v>0.5187056086699035</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.4823897678738026</v>
+        <v>0.4812943913300965</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.60051</v>
+        <v>0.60075</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.237095</v>
+        <v>0.23674</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.162395</v>
+        <v>0.16251</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.534125</v>
+        <v>0.5351900000000001</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.517245</v>
+        <v>0.51833</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.91005</v>
+        <v>1.91315</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.904725</v>
+        <v>0.90673</v>
       </c>
       <c r="AM2" t="n">
-        <v>2.814775</v>
+        <v>2.81988</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.649988328846313</v>
+        <v>0.6496766368162163</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.20670219945167</v>
+        <v>0.2067150167547317</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.143309471702017</v>
+        <v>0.1436083464290519</v>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
         </is>
       </c>
       <c r="AR2" t="n">
-        <v>0.649988328846313</v>
+        <v>0.6496766368162163</v>
       </c>
       <c r="AS2" t="b">
         <v>1</v>
@@ -960,16 +960,16 @@
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>7.454581959171223</v>
+        <v>7.41962011431583</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.143309471702017</v>
+        <v>0.1436083464290519</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.009163787144921248</v>
+        <v>0.008830556651035604</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.06831220232821522</v>
+        <v>0.0655193757486292</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         </is>
       </c>
       <c r="BE2" t="n">
-        <v>0.113953897661469</v>
+        <v>0.1138160465431237</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         </is>
       </c>
       <c r="BG2" t="n">
-        <v>0.1092500572116637</v>
+        <v>0.1090002427663653</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="BI2" t="n">
-        <v>0.1040920719627856</v>
+        <v>0.1036597297533752</v>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>0.09888641173185585</v>
+        <v>0.09892546903999373</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         </is>
       </c>
       <c r="BM2" t="n">
-        <v>0.07030975613784293</v>
+        <v>0.06996840743748034</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         </is>
       </c>
       <c r="BO2" t="n">
-        <v>0.06952332476525568</v>
+        <v>0.06947579312117107</v>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="BQ2" t="n">
-        <v>0.06292822441625802</v>
+        <v>0.06305422122929641</v>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="BS2" t="n">
-        <v>0.04688365359500635</v>
+        <v>0.04695279696298824</v>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="BU2" t="n">
-        <v>0.044752939608338</v>
+        <v>0.0448909478383407</v>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         </is>
       </c>
       <c r="BW2" t="n">
-        <v>0.04390387761579546</v>
+        <v>0.04376383102615729</v>
       </c>
     </row>
     <row r="3">
@@ -1102,40 +1102,40 @@
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8827815686972356</v>
+        <v>0.8842842707993464</v>
       </c>
       <c r="L3" t="n">
-        <v>2.059043805092176</v>
+        <v>2.063041102990065</v>
       </c>
       <c r="M3" t="b">
         <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>0.06871985192605301</v>
+        <v>0.06892192141386622</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1404019187911976</v>
+        <v>0.1403667680384011</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7908782292827493</v>
+        <v>0.7907113105477327</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.589228908137402</v>
+        <v>0.5921365927834542</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6945089467029859</v>
+        <v>0.6972411323431873</v>
       </c>
       <c r="S3" t="n">
-        <v>2.365491053297014</v>
+        <v>2.372758867656812</v>
       </c>
       <c r="T3" t="n">
         <v>0.2349818781757194</v>
       </c>
       <c r="U3" t="n">
-        <v>0.347460682500802</v>
+        <v>0.3474606825008021</v>
       </c>
       <c r="V3" t="n">
-        <v>0.4175574393234786</v>
+        <v>0.4175574393234787</v>
       </c>
       <c r="W3" t="n">
         <v>0.3580113382151557</v>
@@ -1144,58 +1144,58 @@
         <v>0.5032649230659736</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.1421310446546143</v>
+        <v>0.1420374363327333</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.2213402932043935</v>
+        <v>0.2209726553994504</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.6365286621409921</v>
+        <v>0.6369899082678167</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.5636461183409083</v>
+        <v>0.5649008204533689</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.4363538816590917</v>
+        <v>0.4350991795466311</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.5211537464031136</v>
+        <v>0.5219765175944948</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.4788462535968864</v>
+        <v>0.4780234824055052</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.14265</v>
+        <v>0.1427</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.220585</v>
+        <v>0.220075</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.636765</v>
+        <v>0.637225</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.561765</v>
+        <v>0.563125</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.520685</v>
+        <v>0.52146</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.88357</v>
+        <v>0.88515</v>
       </c>
       <c r="AL3" t="n">
-        <v>2.0573</v>
+        <v>2.060465</v>
       </c>
       <c r="AM3" t="n">
-        <v>2.94087</v>
+        <v>2.945615</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.1452643592955766</v>
+        <v>0.1453217850102316</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.2331070796928582</v>
+        <v>0.2330011099405038</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6216285610115653</v>
+        <v>0.6216771050492648</v>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="AR3" t="n">
-        <v>0.6216285610115653</v>
+        <v>0.6216771050492648</v>
       </c>
       <c r="AS3" t="b">
         <v>1</v>
@@ -1214,16 +1214,16 @@
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>14.55183577921652</v>
+        <v>14.50917182060471</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.1452643592955766</v>
+        <v>0.1453217850102316</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.07654450736952355</v>
+        <v>0.07639986359636537</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.113863101042336</v>
+        <v>1.108498747990428</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
@@ -1231,16 +1231,16 @@
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>7.122409783353288</v>
+        <v>7.124193382627596</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.2331070796928582</v>
+        <v>0.2330011099405038</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.0927051609016605</v>
+        <v>0.09263434190210268</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.6602841449733274</v>
+        <v>0.6599449655830223</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         </is>
       </c>
       <c r="BE3" t="n">
-        <v>0.111863231841484</v>
+        <v>0.111682060057284</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
@@ -1256,23 +1256,23 @@
         </is>
       </c>
       <c r="BG3" t="n">
-        <v>0.1055109939326054</v>
+        <v>0.1053149719465961</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="BI3" t="n">
+        <v>0.09875868903912419</v>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
           <t>0-1</t>
         </is>
       </c>
-      <c r="BI3" t="n">
-        <v>0.09906360579682921</v>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>1-2</t>
-        </is>
-      </c>
       <c r="BK3" t="n">
-        <v>0.09875079928456783</v>
+        <v>0.09869526206319298</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="BM3" t="n">
-        <v>0.07677709818026583</v>
+        <v>0.07680156012159393</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="BO3" t="n">
-        <v>0.06777740717159675</v>
+        <v>0.06791441158837586</v>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         </is>
       </c>
       <c r="BQ3" t="n">
-        <v>0.06236179816840872</v>
+        <v>0.0620545504615745</v>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         </is>
       </c>
       <c r="BS3" t="n">
-        <v>0.04358769275126832</v>
+        <v>0.04366537766103067</v>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         </is>
       </c>
       <c r="BU3" t="n">
-        <v>0.04233780033574086</v>
+        <v>0.04233107871456786</v>
       </c>
       <c r="BV3" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         </is>
       </c>
       <c r="BW3" t="n">
-        <v>0.03952185209525753</v>
+        <v>0.03961119382615272</v>
       </c>
     </row>
     <row r="4">
@@ -1388,13 +1388,13 @@
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="n">
-        <v>0.7564763819784712</v>
+        <v>0.7564763819784714</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1576579982791547</v>
+        <v>0.1576579982791548</v>
       </c>
       <c r="V4" t="n">
-        <v>0.08586561974237397</v>
+        <v>0.08586561974237394</v>
       </c>
       <c r="W4" t="n">
         <v>0.5767361239417156</v>
